--- a/artfynd/A 6960-2025 artfynd.xlsx
+++ b/artfynd/A 6960-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126003883</v>
       </c>
       <c r="B2" t="n">
-        <v>109144</v>
+        <v>109145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126003888</v>
       </c>
       <c r="B3" t="n">
-        <v>109144</v>
+        <v>109145</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>126003885</v>
       </c>
       <c r="B4" t="n">
-        <v>109144</v>
+        <v>109145</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,54 +1005,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126003891</v>
+        <v>126003878</v>
       </c>
       <c r="B5" t="n">
-        <v>99006</v>
+        <v>98310</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222322</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Butrajvs 1:15 (2), Gtl</t>
+          <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720349</v>
+        <v>720409</v>
       </c>
       <c r="R5" t="n">
-        <v>6383491</v>
+        <v>6383367</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1085,11 +1085,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126003884</v>
+        <v>126003891</v>
       </c>
       <c r="B6" t="n">
-        <v>99006</v>
+        <v>99007</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,7 +1146,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1165,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720341</v>
+        <v>720349</v>
       </c>
       <c r="R6" t="n">
-        <v>6383430</v>
+        <v>6383491</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1201,6 +1196,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,54 +1232,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126003878</v>
+        <v>126003884</v>
       </c>
       <c r="B7" t="n">
-        <v>98309</v>
+        <v>99007</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>222322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Burs 1:3 (1), Gtl</t>
+          <t>Butrajvs 1:15 (2), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720409</v>
+        <v>720341</v>
       </c>
       <c r="R7" t="n">
-        <v>6383367</v>
+        <v>6383430</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1346,7 +1346,7 @@
         <v>126003874</v>
       </c>
       <c r="B8" t="n">
-        <v>109144</v>
+        <v>109145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>126003890</v>
       </c>
       <c r="B9" t="n">
-        <v>109144</v>
+        <v>109145</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>126003893</v>
       </c>
       <c r="B10" t="n">
-        <v>109144</v>
+        <v>109145</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>126003887</v>
       </c>
       <c r="B11" t="n">
-        <v>109144</v>
+        <v>109145</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126003886</v>
+        <v>126004109</v>
       </c>
       <c r="B12" t="n">
-        <v>99006</v>
+        <v>57648</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,31 +1781,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222322</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720346</v>
+        <v>720334</v>
       </c>
       <c r="R12" t="n">
-        <v>6383450</v>
+        <v>6383480</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1852,6 +1852,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Spillkråkehack i död tall.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1863,7 +1868,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Tallsumpskog med en, blåtåtel.</t>
+          <t>Kalklbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1881,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126004109</v>
+        <v>126003886</v>
       </c>
       <c r="B13" t="n">
-        <v>57648</v>
+        <v>99007</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,31 +1897,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>222322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1925,10 +1930,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720334</v>
+        <v>720346</v>
       </c>
       <c r="R13" t="n">
-        <v>6383480</v>
+        <v>6383450</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1963,11 +1968,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spillkråkehack i död tall.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalklbarrskog med kontinuitet.</t>
+          <t>Tallsumpskog med en, blåtåtel.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2000,7 +2000,7 @@
         <v>126003880</v>
       </c>
       <c r="B14" t="n">
-        <v>109144</v>
+        <v>109145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>126003877</v>
       </c>
       <c r="B15" t="n">
-        <v>98309</v>
+        <v>98310</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>126003896</v>
       </c>
       <c r="B16" t="n">
-        <v>98309</v>
+        <v>98310</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>126003879</v>
       </c>
       <c r="B17" t="n">
-        <v>109144</v>
+        <v>109145</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>126003875</v>
       </c>
       <c r="B18" t="n">
-        <v>99006</v>
+        <v>99007</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,33 +2536,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126003872</v>
+        <v>126003870</v>
       </c>
       <c r="B19" t="n">
-        <v>98242</v>
+        <v>105254</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223578</v>
+        <v>221137</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Äkta ängsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. incarnata</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2582,7 +2586,7 @@
         <v>6383301</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2616,7 +2620,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Tre mörkblommiga.</t>
+          <t>Uppskattat antal.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2648,37 +2652,33 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126003870</v>
+        <v>126003872</v>
       </c>
       <c r="B20" t="n">
-        <v>105253</v>
+        <v>98243</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221137</v>
+        <v>223578</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Äkta ängsnycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2698,7 +2698,7 @@
         <v>6383301</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Uppskattat antal.</t>
+          <t>Tre mörkblommiga.</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 6960-2025 artfynd.xlsx
+++ b/artfynd/A 6960-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126003883</v>
       </c>
       <c r="B2" t="n">
-        <v>109145</v>
+        <v>109147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126003888</v>
       </c>
       <c r="B3" t="n">
-        <v>109145</v>
+        <v>109147</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>126003885</v>
       </c>
       <c r="B4" t="n">
-        <v>109145</v>
+        <v>109147</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>126003878</v>
       </c>
       <c r="B5" t="n">
-        <v>98310</v>
+        <v>98312</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>126003891</v>
       </c>
       <c r="B6" t="n">
-        <v>99007</v>
+        <v>99009</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>126003884</v>
       </c>
       <c r="B7" t="n">
-        <v>99007</v>
+        <v>99009</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>126003874</v>
       </c>
       <c r="B8" t="n">
-        <v>109145</v>
+        <v>109147</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>126003890</v>
       </c>
       <c r="B9" t="n">
-        <v>109145</v>
+        <v>109147</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>126003893</v>
       </c>
       <c r="B10" t="n">
-        <v>109145</v>
+        <v>109147</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>126003887</v>
       </c>
       <c r="B11" t="n">
-        <v>109145</v>
+        <v>109147</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>126003886</v>
       </c>
       <c r="B13" t="n">
-        <v>99007</v>
+        <v>99009</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>126003880</v>
       </c>
       <c r="B14" t="n">
-        <v>109145</v>
+        <v>109147</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>126003877</v>
       </c>
       <c r="B15" t="n">
-        <v>98310</v>
+        <v>98312</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>126003896</v>
       </c>
       <c r="B16" t="n">
-        <v>98310</v>
+        <v>98312</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>126003879</v>
       </c>
       <c r="B17" t="n">
-        <v>109145</v>
+        <v>109147</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>126003875</v>
       </c>
       <c r="B18" t="n">
-        <v>99007</v>
+        <v>99009</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,37 +2536,33 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126003870</v>
+        <v>126003872</v>
       </c>
       <c r="B19" t="n">
-        <v>105254</v>
+        <v>98245</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221137</v>
+        <v>223578</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Äkta ängsnycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2586,7 +2582,7 @@
         <v>6383301</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2620,7 +2616,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Uppskattat antal.</t>
+          <t>Tre mörkblommiga.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2652,33 +2648,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126003872</v>
+        <v>126003870</v>
       </c>
       <c r="B20" t="n">
-        <v>98243</v>
+        <v>105256</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223578</v>
+        <v>221137</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Äkta ängsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. incarnata</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2698,7 +2698,7 @@
         <v>6383301</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Tre mörkblommiga.</t>
+          <t>Uppskattat antal.</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 6960-2025 artfynd.xlsx
+++ b/artfynd/A 6960-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126003883</v>
       </c>
       <c r="B2" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126003888</v>
       </c>
       <c r="B3" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>126003885</v>
       </c>
       <c r="B4" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,54 +1005,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126003878</v>
+        <v>126003891</v>
       </c>
       <c r="B5" t="n">
-        <v>98312</v>
+        <v>99013</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>222322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Burs 1:3 (1), Gtl</t>
+          <t>Butrajvs 1:15 (2), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720409</v>
+        <v>720349</v>
       </c>
       <c r="R5" t="n">
-        <v>6383367</v>
+        <v>6383491</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1085,6 +1085,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126003891</v>
+        <v>126003884</v>
       </c>
       <c r="B6" t="n">
-        <v>99009</v>
+        <v>99013</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1146,7 +1151,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1160,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720349</v>
+        <v>720341</v>
       </c>
       <c r="R6" t="n">
-        <v>6383491</v>
+        <v>6383430</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1196,11 +1201,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,54 +1232,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126003884</v>
+        <v>126003878</v>
       </c>
       <c r="B7" t="n">
-        <v>99009</v>
+        <v>98316</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222322</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Butrajvs 1:15 (2), Gtl</t>
+          <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720341</v>
+        <v>720409</v>
       </c>
       <c r="R7" t="n">
-        <v>6383430</v>
+        <v>6383367</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1346,7 +1346,7 @@
         <v>126003874</v>
       </c>
       <c r="B8" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>126003890</v>
       </c>
       <c r="B9" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>126003893</v>
       </c>
       <c r="B10" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>126003887</v>
       </c>
       <c r="B11" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>126003886</v>
       </c>
       <c r="B13" t="n">
-        <v>99009</v>
+        <v>99013</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>126003880</v>
       </c>
       <c r="B14" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>126003877</v>
       </c>
       <c r="B15" t="n">
-        <v>98312</v>
+        <v>98316</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>126003896</v>
       </c>
       <c r="B16" t="n">
-        <v>98312</v>
+        <v>98316</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>126003879</v>
       </c>
       <c r="B17" t="n">
-        <v>109147</v>
+        <v>109151</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>126003875</v>
       </c>
       <c r="B18" t="n">
-        <v>99009</v>
+        <v>99013</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>126003872</v>
       </c>
       <c r="B19" t="n">
-        <v>98245</v>
+        <v>98249</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>126003870</v>
       </c>
       <c r="B20" t="n">
-        <v>105256</v>
+        <v>105260</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 6960-2025 artfynd.xlsx
+++ b/artfynd/A 6960-2025 artfynd.xlsx
@@ -2536,33 +2536,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126003872</v>
+        <v>126003870</v>
       </c>
       <c r="B19" t="n">
-        <v>98249</v>
+        <v>105260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223578</v>
+        <v>221137</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Äkta ängsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. incarnata</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2582,7 +2586,7 @@
         <v>6383301</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2616,7 +2620,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Tre mörkblommiga.</t>
+          <t>Uppskattat antal.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2648,37 +2652,33 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126003870</v>
+        <v>126003872</v>
       </c>
       <c r="B20" t="n">
-        <v>105260</v>
+        <v>98249</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221137</v>
+        <v>223578</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Äkta ängsnycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2698,7 +2698,7 @@
         <v>6383301</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Uppskattat antal.</t>
+          <t>Tre mörkblommiga.</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 6960-2025 artfynd.xlsx
+++ b/artfynd/A 6960-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126003883</v>
       </c>
       <c r="B2" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126003888</v>
       </c>
       <c r="B3" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>126003885</v>
       </c>
       <c r="B4" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,54 +1005,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126003891</v>
+        <v>126003878</v>
       </c>
       <c r="B5" t="n">
-        <v>99013</v>
+        <v>98317</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222322</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Butrajvs 1:15 (2), Gtl</t>
+          <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720349</v>
+        <v>720409</v>
       </c>
       <c r="R5" t="n">
-        <v>6383491</v>
+        <v>6383367</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1085,11 +1085,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126003884</v>
+        <v>126003891</v>
       </c>
       <c r="B6" t="n">
-        <v>99013</v>
+        <v>99014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,7 +1146,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1165,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720341</v>
+        <v>720349</v>
       </c>
       <c r="R6" t="n">
-        <v>6383430</v>
+        <v>6383491</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1201,6 +1196,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,54 +1232,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126003878</v>
+        <v>126003884</v>
       </c>
       <c r="B7" t="n">
-        <v>98316</v>
+        <v>99014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>222322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Burs 1:3 (1), Gtl</t>
+          <t>Butrajvs 1:15 (2), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720409</v>
+        <v>720341</v>
       </c>
       <c r="R7" t="n">
-        <v>6383367</v>
+        <v>6383430</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1346,7 +1346,7 @@
         <v>126003874</v>
       </c>
       <c r="B8" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>126003890</v>
       </c>
       <c r="B9" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>126003893</v>
       </c>
       <c r="B10" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>126003887</v>
       </c>
       <c r="B11" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>126003886</v>
       </c>
       <c r="B13" t="n">
-        <v>99013</v>
+        <v>99014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>126003880</v>
       </c>
       <c r="B14" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>126003877</v>
       </c>
       <c r="B15" t="n">
-        <v>98316</v>
+        <v>98317</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>126003896</v>
       </c>
       <c r="B16" t="n">
-        <v>98316</v>
+        <v>98317</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>126003879</v>
       </c>
       <c r="B17" t="n">
-        <v>109151</v>
+        <v>109152</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>126003875</v>
       </c>
       <c r="B18" t="n">
-        <v>99013</v>
+        <v>99014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,37 +2536,33 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126003870</v>
+        <v>126003872</v>
       </c>
       <c r="B19" t="n">
-        <v>105260</v>
+        <v>98250</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221137</v>
+        <v>223578</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Äkta ängsnycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2586,7 +2582,7 @@
         <v>6383301</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2620,7 +2616,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Uppskattat antal.</t>
+          <t>Tre mörkblommiga.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2652,33 +2648,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126003872</v>
+        <v>126003870</v>
       </c>
       <c r="B20" t="n">
-        <v>98249</v>
+        <v>105261</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223578</v>
+        <v>221137</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Äkta ängsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. incarnata</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2698,7 +2698,7 @@
         <v>6383301</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Tre mörkblommiga.</t>
+          <t>Uppskattat antal.</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 6960-2025 artfynd.xlsx
+++ b/artfynd/A 6960-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2762,6 +2762,224 @@
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126192141</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98375</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Butrajvs 1:15 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>720284</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6383392</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Avverkningsväg äldre, med körspår.</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126192151</v>
+      </c>
+      <c r="B22" t="n">
+        <v>109152</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Butrajvs 1:15 (2), Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>720283</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6383284</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norrlanda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Avverkningsväg äldre, med körspår.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 6960-2025 artfynd.xlsx
+++ b/artfynd/A 6960-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126003883</v>
+        <v>126003888</v>
       </c>
       <c r="B2" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -703,17 +703,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Butrajvs 1:15 (2), Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720385</v>
+        <v>720347</v>
       </c>
       <c r="R2" t="n">
-        <v>6383405</v>
+        <v>6383465</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Spridd. Minstaa ntal.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126003888</v>
+        <v>126003883</v>
       </c>
       <c r="B3" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -810,26 +819,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Butrajvs 1:15 (2), Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720347</v>
+        <v>720385</v>
       </c>
       <c r="R3" t="n">
-        <v>6383465</v>
+        <v>6383405</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Spridd. Minstaa ntal.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,7 +901,7 @@
         <v>126003885</v>
       </c>
       <c r="B4" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>126003878</v>
       </c>
       <c r="B5" t="n">
-        <v>98317</v>
+        <v>98319</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>126003891</v>
       </c>
       <c r="B6" t="n">
-        <v>99014</v>
+        <v>99016</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>126003884</v>
       </c>
       <c r="B7" t="n">
-        <v>99014</v>
+        <v>99016</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>126003874</v>
       </c>
       <c r="B8" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>126003890</v>
       </c>
       <c r="B9" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>126003893</v>
       </c>
       <c r="B10" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>126003887</v>
       </c>
       <c r="B11" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126004109</v>
+        <v>126003886</v>
       </c>
       <c r="B12" t="n">
-        <v>57648</v>
+        <v>99016</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,31 +1781,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>222322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720334</v>
+        <v>720346</v>
       </c>
       <c r="R12" t="n">
-        <v>6383480</v>
+        <v>6383450</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1852,11 +1852,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Spillkråkehack i död tall.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1868,7 +1863,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalklbarrskog med kontinuitet.</t>
+          <t>Tallsumpskog med en, blåtåtel.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1886,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126003886</v>
+        <v>126004109</v>
       </c>
       <c r="B13" t="n">
-        <v>99014</v>
+        <v>57649</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,31 +1892,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222322</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1930,10 +1925,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720346</v>
+        <v>720334</v>
       </c>
       <c r="R13" t="n">
-        <v>6383450</v>
+        <v>6383480</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1968,6 +1963,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillkråkehack i död tall.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Tallsumpskog med en, blåtåtel.</t>
+          <t>Kalklbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -1997,32 +1997,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126003880</v>
+        <v>126003877</v>
       </c>
       <c r="B14" t="n">
-        <v>109152</v>
+        <v>98319</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720395</v>
+        <v>720418</v>
       </c>
       <c r="R14" t="n">
-        <v>6383383</v>
+        <v>6383301</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2070,11 +2070,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2086,7 +2081,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Tallsumpskog med en, blåtåtel.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2104,32 +2099,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126003877</v>
+        <v>126003880</v>
       </c>
       <c r="B15" t="n">
-        <v>98317</v>
+        <v>109154</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2139,10 +2134,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720418</v>
+        <v>720395</v>
       </c>
       <c r="R15" t="n">
-        <v>6383301</v>
+        <v>6383383</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2177,6 +2172,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Tallsumpskog med en, blåtåtel.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2209,7 +2209,7 @@
         <v>126003896</v>
       </c>
       <c r="B16" t="n">
-        <v>98317</v>
+        <v>98319</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>126003879</v>
       </c>
       <c r="B17" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>126003875</v>
       </c>
       <c r="B18" t="n">
-        <v>99014</v>
+        <v>99016</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>126003872</v>
       </c>
       <c r="B19" t="n">
-        <v>98250</v>
+        <v>98252</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>126003870</v>
       </c>
       <c r="B20" t="n">
-        <v>105261</v>
+        <v>105263</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>126192141</v>
       </c>
       <c r="B21" t="n">
-        <v>98375</v>
+        <v>98377</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>126192151</v>
       </c>
       <c r="B22" t="n">
-        <v>109152</v>
+        <v>109154</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 6960-2025 artfynd.xlsx
+++ b/artfynd/A 6960-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126003888</v>
+        <v>126003883</v>
       </c>
       <c r="B2" t="n">
         <v>109154</v>
@@ -703,26 +703,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Butrajvs 1:15 (2), Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720347</v>
+        <v>720385</v>
       </c>
       <c r="R2" t="n">
-        <v>6383465</v>
+        <v>6383405</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spridd. Minstaa ntal.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126003883</v>
+        <v>126003888</v>
       </c>
       <c r="B3" t="n">
         <v>109154</v>
@@ -819,17 +810,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Butrajvs 1:15 (2), Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720385</v>
+        <v>720347</v>
       </c>
       <c r="R3" t="n">
-        <v>6383405</v>
+        <v>6383465</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Spridd. Minstaa ntal.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126003886</v>
+        <v>126004109</v>
       </c>
       <c r="B12" t="n">
-        <v>99016</v>
+        <v>57649</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,31 +1781,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222322</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720346</v>
+        <v>720334</v>
       </c>
       <c r="R12" t="n">
-        <v>6383450</v>
+        <v>6383480</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1852,6 +1852,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Spillkråkehack i död tall.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1863,7 +1868,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Tallsumpskog med en, blåtåtel.</t>
+          <t>Kalklbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1881,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126004109</v>
+        <v>126003886</v>
       </c>
       <c r="B13" t="n">
-        <v>57649</v>
+        <v>99016</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,31 +1897,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>222322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1925,10 +1930,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720334</v>
+        <v>720346</v>
       </c>
       <c r="R13" t="n">
-        <v>6383480</v>
+        <v>6383450</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1963,11 +1968,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spillkråkehack i död tall.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalklbarrskog med kontinuitet.</t>
+          <t>Tallsumpskog med en, blåtåtel.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>

--- a/artfynd/A 6960-2025 artfynd.xlsx
+++ b/artfynd/A 6960-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126003883</v>
       </c>
       <c r="B2" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126003888</v>
       </c>
       <c r="B3" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>126003885</v>
       </c>
       <c r="B4" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,54 +1005,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126003878</v>
+        <v>126003891</v>
       </c>
       <c r="B5" t="n">
-        <v>98319</v>
+        <v>99018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>222322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Burs 1:3 (1), Gtl</t>
+          <t>Butrajvs 1:15 (2), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720409</v>
+        <v>720349</v>
       </c>
       <c r="R5" t="n">
-        <v>6383367</v>
+        <v>6383491</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1085,6 +1085,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126003891</v>
+        <v>126003884</v>
       </c>
       <c r="B6" t="n">
-        <v>99016</v>
+        <v>99018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1146,7 +1151,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1160,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720349</v>
+        <v>720341</v>
       </c>
       <c r="R6" t="n">
-        <v>6383491</v>
+        <v>6383430</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1196,11 +1201,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,54 +1232,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126003884</v>
+        <v>126003878</v>
       </c>
       <c r="B7" t="n">
-        <v>99016</v>
+        <v>98321</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222322</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Butrajvs 1:15 (2), Gtl</t>
+          <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720341</v>
+        <v>720409</v>
       </c>
       <c r="R7" t="n">
-        <v>6383430</v>
+        <v>6383367</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1346,7 +1346,7 @@
         <v>126003874</v>
       </c>
       <c r="B8" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>126003890</v>
       </c>
       <c r="B9" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>126003893</v>
       </c>
       <c r="B10" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>126003887</v>
       </c>
       <c r="B11" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>126003886</v>
       </c>
       <c r="B13" t="n">
-        <v>99016</v>
+        <v>99018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>126003877</v>
       </c>
       <c r="B14" t="n">
-        <v>98319</v>
+        <v>98321</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>126003880</v>
       </c>
       <c r="B15" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>126003896</v>
       </c>
       <c r="B16" t="n">
-        <v>98319</v>
+        <v>98321</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>126003879</v>
       </c>
       <c r="B17" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>126003875</v>
       </c>
       <c r="B18" t="n">
-        <v>99016</v>
+        <v>99018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,33 +2536,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126003872</v>
+        <v>126003870</v>
       </c>
       <c r="B19" t="n">
-        <v>98252</v>
+        <v>105265</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223578</v>
+        <v>221137</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Äkta ängsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. incarnata</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2582,7 +2586,7 @@
         <v>6383301</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2616,7 +2620,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Tre mörkblommiga.</t>
+          <t>Uppskattat antal.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2648,37 +2652,33 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126003870</v>
+        <v>126003872</v>
       </c>
       <c r="B20" t="n">
-        <v>105263</v>
+        <v>98254</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221137</v>
+        <v>223578</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Äkta ängsnycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2698,7 +2698,7 @@
         <v>6383301</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Uppskattat antal.</t>
+          <t>Tre mörkblommiga.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2767,7 +2767,7 @@
         <v>126192141</v>
       </c>
       <c r="B21" t="n">
-        <v>98377</v>
+        <v>98379</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>126192151</v>
       </c>
       <c r="B22" t="n">
-        <v>109154</v>
+        <v>109156</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 6960-2025 artfynd.xlsx
+++ b/artfynd/A 6960-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126003883</v>
       </c>
       <c r="B2" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126003888</v>
       </c>
       <c r="B3" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>126003885</v>
       </c>
       <c r="B4" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1005,54 +1005,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126003891</v>
+        <v>126003878</v>
       </c>
       <c r="B5" t="n">
-        <v>99018</v>
+        <v>98323</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222322</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Butrajvs 1:15 (2), Gtl</t>
+          <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720349</v>
+        <v>720409</v>
       </c>
       <c r="R5" t="n">
-        <v>6383491</v>
+        <v>6383367</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1085,11 +1085,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126003884</v>
+        <v>126003891</v>
       </c>
       <c r="B6" t="n">
-        <v>99018</v>
+        <v>99020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,7 +1146,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1165,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720341</v>
+        <v>720349</v>
       </c>
       <c r="R6" t="n">
-        <v>6383430</v>
+        <v>6383491</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1201,6 +1196,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,54 +1232,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126003878</v>
+        <v>126003884</v>
       </c>
       <c r="B7" t="n">
-        <v>98321</v>
+        <v>99020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>222322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Burs 1:3 (1), Gtl</t>
+          <t>Butrajvs 1:15 (2), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720409</v>
+        <v>720341</v>
       </c>
       <c r="R7" t="n">
-        <v>6383367</v>
+        <v>6383430</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1346,7 +1346,7 @@
         <v>126003874</v>
       </c>
       <c r="B8" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>126003890</v>
       </c>
       <c r="B9" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>126003893</v>
       </c>
       <c r="B10" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>126003887</v>
       </c>
       <c r="B11" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>126003886</v>
       </c>
       <c r="B13" t="n">
-        <v>99018</v>
+        <v>99020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,32 +1997,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126003877</v>
+        <v>126003880</v>
       </c>
       <c r="B14" t="n">
-        <v>98321</v>
+        <v>109160</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720418</v>
+        <v>720395</v>
       </c>
       <c r="R14" t="n">
-        <v>6383301</v>
+        <v>6383383</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2070,6 +2070,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2081,7 +2086,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Tallsumpskog med en, blåtåtel.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2099,32 +2104,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126003880</v>
+        <v>126003877</v>
       </c>
       <c r="B15" t="n">
-        <v>109156</v>
+        <v>98323</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2134,10 +2139,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720395</v>
+        <v>720418</v>
       </c>
       <c r="R15" t="n">
-        <v>6383383</v>
+        <v>6383301</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2172,11 +2177,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Tallsumpskog med en, blåtåtel.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2209,7 +2209,7 @@
         <v>126003896</v>
       </c>
       <c r="B16" t="n">
-        <v>98321</v>
+        <v>98323</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>126003879</v>
       </c>
       <c r="B17" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>126003875</v>
       </c>
       <c r="B18" t="n">
-        <v>99018</v>
+        <v>99020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,37 +2536,33 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126003870</v>
+        <v>126003872</v>
       </c>
       <c r="B19" t="n">
-        <v>105265</v>
+        <v>98256</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221137</v>
+        <v>223578</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Äkta ängsnycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2586,7 +2582,7 @@
         <v>6383301</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2620,7 +2616,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Uppskattat antal.</t>
+          <t>Tre mörkblommiga.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2652,33 +2648,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126003872</v>
+        <v>126003870</v>
       </c>
       <c r="B20" t="n">
-        <v>98254</v>
+        <v>105269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223578</v>
+        <v>221137</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Äkta ängsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. incarnata</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2698,7 +2698,7 @@
         <v>6383301</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Tre mörkblommiga.</t>
+          <t>Uppskattat antal.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2767,7 +2767,7 @@
         <v>126192141</v>
       </c>
       <c r="B21" t="n">
-        <v>98379</v>
+        <v>98381</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>126192151</v>
       </c>
       <c r="B22" t="n">
-        <v>109156</v>
+        <v>109160</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 6960-2025 artfynd.xlsx
+++ b/artfynd/A 6960-2025 artfynd.xlsx
@@ -2536,33 +2536,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126003872</v>
+        <v>126003870</v>
       </c>
       <c r="B19" t="n">
-        <v>98256</v>
+        <v>105269</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223578</v>
+        <v>221137</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Äkta ängsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. incarnata</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2582,7 +2586,7 @@
         <v>6383301</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2616,7 +2620,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Tre mörkblommiga.</t>
+          <t>Uppskattat antal.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2648,37 +2652,33 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126003870</v>
+        <v>126003872</v>
       </c>
       <c r="B20" t="n">
-        <v>105269</v>
+        <v>98256</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221137</v>
+        <v>223578</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Äkta ängsnycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2698,7 +2698,7 @@
         <v>6383301</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Uppskattat antal.</t>
+          <t>Tre mörkblommiga.</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 6960-2025 artfynd.xlsx
+++ b/artfynd/A 6960-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126003883</v>
       </c>
       <c r="B2" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126003888</v>
       </c>
       <c r="B3" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>126003885</v>
       </c>
       <c r="B4" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>126003878</v>
       </c>
       <c r="B5" t="n">
-        <v>98323</v>
+        <v>98327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>126003891</v>
       </c>
       <c r="B6" t="n">
-        <v>99020</v>
+        <v>99024</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>126003884</v>
       </c>
       <c r="B7" t="n">
-        <v>99020</v>
+        <v>99024</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>126003874</v>
       </c>
       <c r="B8" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>126003890</v>
       </c>
       <c r="B9" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>126003893</v>
       </c>
       <c r="B10" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>126003887</v>
       </c>
       <c r="B11" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>126004109</v>
       </c>
       <c r="B12" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>126003886</v>
       </c>
       <c r="B13" t="n">
-        <v>99020</v>
+        <v>99024</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>126003880</v>
       </c>
       <c r="B14" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>126003877</v>
       </c>
       <c r="B15" t="n">
-        <v>98323</v>
+        <v>98327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>126003896</v>
       </c>
       <c r="B16" t="n">
-        <v>98323</v>
+        <v>98327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>126003879</v>
       </c>
       <c r="B17" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>126003875</v>
       </c>
       <c r="B18" t="n">
-        <v>99020</v>
+        <v>99024</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2536,37 +2536,33 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126003870</v>
+        <v>126003872</v>
       </c>
       <c r="B19" t="n">
-        <v>105269</v>
+        <v>98260</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221137</v>
+        <v>223578</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Äkta ängsnycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2586,7 +2582,7 @@
         <v>6383301</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2620,7 +2616,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Uppskattat antal.</t>
+          <t>Tre mörkblommiga.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2652,33 +2648,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126003872</v>
+        <v>126003870</v>
       </c>
       <c r="B20" t="n">
-        <v>98256</v>
+        <v>105282</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223578</v>
+        <v>221137</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Äkta ängsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. incarnata</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2698,7 +2698,7 @@
         <v>6383301</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Tre mörkblommiga.</t>
+          <t>Uppskattat antal.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2767,7 +2767,7 @@
         <v>126192141</v>
       </c>
       <c r="B21" t="n">
-        <v>98381</v>
+        <v>98385</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>126192151</v>
       </c>
       <c r="B22" t="n">
-        <v>109160</v>
+        <v>109173</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 6960-2025 artfynd.xlsx
+++ b/artfynd/A 6960-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126003883</v>
       </c>
       <c r="B2" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126003888</v>
       </c>
       <c r="B3" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>126003885</v>
       </c>
       <c r="B4" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>126003878</v>
       </c>
       <c r="B5" t="n">
-        <v>98327</v>
+        <v>98330</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>126003891</v>
       </c>
       <c r="B6" t="n">
-        <v>99024</v>
+        <v>99027</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>126003884</v>
       </c>
       <c r="B7" t="n">
-        <v>99024</v>
+        <v>99027</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,10 +1343,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126003874</v>
+        <v>126003890</v>
       </c>
       <c r="B8" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,14 +1374,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Burs 1:3 (1), Gtl</t>
+          <t>Butrajvs 1:15 (2), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720418</v>
+        <v>720349</v>
       </c>
       <c r="R8" t="n">
-        <v>6383301</v>
+        <v>6383491</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Tallsumpskog med en, blåtåtel.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1445,10 +1445,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126003890</v>
+        <v>126003874</v>
       </c>
       <c r="B9" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1476,14 +1476,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Butrajvs 1:15 (2), Gtl</t>
+          <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720349</v>
+        <v>720418</v>
       </c>
       <c r="R9" t="n">
-        <v>6383491</v>
+        <v>6383301</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Tallsumpskog med en, blåtåtel.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1550,7 +1550,7 @@
         <v>126003893</v>
       </c>
       <c r="B10" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>126003887</v>
       </c>
       <c r="B11" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>126003886</v>
       </c>
       <c r="B13" t="n">
-        <v>99024</v>
+        <v>99027</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>126003880</v>
       </c>
       <c r="B14" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>126003877</v>
       </c>
       <c r="B15" t="n">
-        <v>98327</v>
+        <v>98330</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>126003896</v>
       </c>
       <c r="B16" t="n">
-        <v>98327</v>
+        <v>98330</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>126003879</v>
       </c>
       <c r="B17" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>126003875</v>
       </c>
       <c r="B18" t="n">
-        <v>99024</v>
+        <v>99027</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>126003872</v>
       </c>
       <c r="B19" t="n">
-        <v>98260</v>
+        <v>98263</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>126003870</v>
       </c>
       <c r="B20" t="n">
-        <v>105282</v>
+        <v>105285</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>126192141</v>
       </c>
       <c r="B21" t="n">
-        <v>98385</v>
+        <v>98388</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>126192151</v>
       </c>
       <c r="B22" t="n">
-        <v>109173</v>
+        <v>109176</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 6960-2025 artfynd.xlsx
+++ b/artfynd/A 6960-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126003883</v>
+        <v>126003888</v>
       </c>
       <c r="B2" t="n">
         <v>109176</v>
@@ -703,17 +703,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Butrajvs 1:15 (2), Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720385</v>
+        <v>720347</v>
       </c>
       <c r="R2" t="n">
-        <v>6383405</v>
+        <v>6383465</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -750,7 +759,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Spridd. Minstaa ntal.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126003888</v>
+        <v>126003883</v>
       </c>
       <c r="B3" t="n">
         <v>109176</v>
@@ -810,26 +819,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Butrajvs 1:15 (2), Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720347</v>
+        <v>720385</v>
       </c>
       <c r="R3" t="n">
-        <v>6383465</v>
+        <v>6383405</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Spridd. Minstaa ntal.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1997,32 +1997,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126003880</v>
+        <v>126003877</v>
       </c>
       <c r="B14" t="n">
-        <v>109176</v>
+        <v>98330</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720395</v>
+        <v>720418</v>
       </c>
       <c r="R14" t="n">
-        <v>6383383</v>
+        <v>6383301</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2070,11 +2070,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2086,7 +2081,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Tallsumpskog med en, blåtåtel.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2104,32 +2099,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126003877</v>
+        <v>126003880</v>
       </c>
       <c r="B15" t="n">
-        <v>98330</v>
+        <v>109176</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2139,10 +2134,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720418</v>
+        <v>720395</v>
       </c>
       <c r="R15" t="n">
-        <v>6383301</v>
+        <v>6383383</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2177,6 +2172,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Tallsumpskog med en, blåtåtel.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 6960-2025 artfynd.xlsx
+++ b/artfynd/A 6960-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126003888</v>
+        <v>126003883</v>
       </c>
       <c r="B2" t="n">
         <v>109176</v>
@@ -703,26 +703,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Butrajvs 1:15 (2), Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720347</v>
+        <v>720385</v>
       </c>
       <c r="R2" t="n">
-        <v>6383465</v>
+        <v>6383405</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,7 +750,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Spridd. Minstaa ntal.</t>
+          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126003883</v>
+        <v>126003888</v>
       </c>
       <c r="B3" t="n">
         <v>109176</v>
@@ -819,17 +810,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Butrajvs 1:15 (2), Gtl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720385</v>
+        <v>720347</v>
       </c>
       <c r="R3" t="n">
-        <v>6383405</v>
+        <v>6383465</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -866,7 +866,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Spridd.</t>
+          <t>Spridd. Minstaa ntal.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1343,7 +1343,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126003890</v>
+        <v>126003874</v>
       </c>
       <c r="B8" t="n">
         <v>109176</v>
@@ -1374,14 +1374,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Butrajvs 1:15 (2), Gtl</t>
+          <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720349</v>
+        <v>720418</v>
       </c>
       <c r="R8" t="n">
-        <v>6383491</v>
+        <v>6383301</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Tallsumpskog med en, blåtåtel.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1445,7 +1445,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126003874</v>
+        <v>126003890</v>
       </c>
       <c r="B9" t="n">
         <v>109176</v>
@@ -1476,14 +1476,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Burs 1:3 (1), Gtl</t>
+          <t>Butrajvs 1:15 (2), Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720418</v>
+        <v>720349</v>
       </c>
       <c r="R9" t="n">
-        <v>6383301</v>
+        <v>6383491</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1529,7 +1529,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Tallsumpskog med en, blåtåtel.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126004109</v>
+        <v>126003886</v>
       </c>
       <c r="B12" t="n">
-        <v>57653</v>
+        <v>99027</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,31 +1781,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>222322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720334</v>
+        <v>720346</v>
       </c>
       <c r="R12" t="n">
-        <v>6383480</v>
+        <v>6383450</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1852,11 +1852,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Spillkråkehack i död tall.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1868,7 +1863,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Kalklbarrskog med kontinuitet.</t>
+          <t>Tallsumpskog med en, blåtåtel.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1886,10 +1881,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126003886</v>
+        <v>126004109</v>
       </c>
       <c r="B13" t="n">
-        <v>99027</v>
+        <v>57653</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,31 +1892,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222322</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1930,10 +1925,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720346</v>
+        <v>720334</v>
       </c>
       <c r="R13" t="n">
-        <v>6383450</v>
+        <v>6383480</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1968,6 +1963,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Spillkråkehack i död tall.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Tallsumpskog med en, blåtåtel.</t>
+          <t>Kalklbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2536,33 +2536,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126003872</v>
+        <v>126003870</v>
       </c>
       <c r="B19" t="n">
-        <v>98263</v>
+        <v>105285</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223578</v>
+        <v>221137</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Äkta ängsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. incarnata</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2582,7 +2586,7 @@
         <v>6383301</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2616,7 +2620,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Tre mörkblommiga.</t>
+          <t>Uppskattat antal.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2648,37 +2652,33 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126003870</v>
+        <v>126003872</v>
       </c>
       <c r="B20" t="n">
-        <v>105285</v>
+        <v>98263</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221137</v>
+        <v>223578</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Äkta ängsnycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2698,7 +2698,7 @@
         <v>6383301</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Uppskattat antal.</t>
+          <t>Tre mörkblommiga.</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 6960-2025 artfynd.xlsx
+++ b/artfynd/A 6960-2025 artfynd.xlsx
@@ -1770,10 +1770,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126003886</v>
+        <v>126004109</v>
       </c>
       <c r="B12" t="n">
-        <v>99027</v>
+        <v>57653</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1781,31 +1781,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222322</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>720346</v>
+        <v>720334</v>
       </c>
       <c r="R12" t="n">
-        <v>6383450</v>
+        <v>6383480</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1852,6 +1852,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Spillkråkehack i död tall.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1863,7 +1868,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Tallsumpskog med en, blåtåtel.</t>
+          <t>Kalklbarrskog med kontinuitet.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -1881,10 +1886,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126004109</v>
+        <v>126003886</v>
       </c>
       <c r="B13" t="n">
-        <v>57653</v>
+        <v>99027</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,31 +1897,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>222322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1925,10 +1930,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>720334</v>
+        <v>720346</v>
       </c>
       <c r="R13" t="n">
-        <v>6383480</v>
+        <v>6383450</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1963,11 +1968,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Spillkråkehack i död tall.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalklbarrskog med kontinuitet.</t>
+          <t>Tallsumpskog med en, blåtåtel.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2536,37 +2536,33 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126003870</v>
+        <v>126003872</v>
       </c>
       <c r="B19" t="n">
-        <v>105285</v>
+        <v>98263</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221137</v>
+        <v>223578</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Äkta ängsnycklar</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2586,7 +2582,7 @@
         <v>6383301</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2620,7 +2616,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Uppskattat antal.</t>
+          <t>Tre mörkblommiga.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2652,33 +2648,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126003872</v>
+        <v>126003870</v>
       </c>
       <c r="B20" t="n">
-        <v>98263</v>
+        <v>105285</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>223578</v>
+        <v>221137</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Äkta ängsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. incarnata</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr"/>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2698,7 +2698,7 @@
         <v>6383301</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Tre mörkblommiga.</t>
+          <t>Uppskattat antal.</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 6960-2025 artfynd.xlsx
+++ b/artfynd/A 6960-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126003883</v>
       </c>
       <c r="B2" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>126003888</v>
       </c>
       <c r="B3" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>126003885</v>
       </c>
       <c r="B4" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
         <v>126003878</v>
       </c>
       <c r="B5" t="n">
-        <v>98330</v>
+        <v>98339</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>126003891</v>
       </c>
       <c r="B6" t="n">
-        <v>99027</v>
+        <v>99036</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>126003884</v>
       </c>
       <c r="B7" t="n">
-        <v>99027</v>
+        <v>99036</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1346,7 +1346,7 @@
         <v>126003874</v>
       </c>
       <c r="B8" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>126003890</v>
       </c>
       <c r="B9" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>126003893</v>
       </c>
       <c r="B10" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>126003887</v>
       </c>
       <c r="B11" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>126004109</v>
       </c>
       <c r="B12" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1889,7 +1889,7 @@
         <v>126003886</v>
       </c>
       <c r="B13" t="n">
-        <v>99027</v>
+        <v>99036</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>126003877</v>
       </c>
       <c r="B14" t="n">
-        <v>98330</v>
+        <v>98339</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         <v>126003880</v>
       </c>
       <c r="B15" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>126003896</v>
       </c>
       <c r="B16" t="n">
-        <v>98330</v>
+        <v>98339</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2325,7 +2325,7 @@
         <v>126003879</v>
       </c>
       <c r="B17" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2432,7 +2432,7 @@
         <v>126003875</v>
       </c>
       <c r="B18" t="n">
-        <v>99027</v>
+        <v>99036</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2539,7 +2539,7 @@
         <v>126003872</v>
       </c>
       <c r="B19" t="n">
-        <v>98263</v>
+        <v>98272</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>126003870</v>
       </c>
       <c r="B20" t="n">
-        <v>105285</v>
+        <v>105294</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         <v>126192141</v>
       </c>
       <c r="B21" t="n">
-        <v>98388</v>
+        <v>98397</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2878,7 +2878,7 @@
         <v>126192151</v>
       </c>
       <c r="B22" t="n">
-        <v>109176</v>
+        <v>109185</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 6960-2025 artfynd.xlsx
+++ b/artfynd/A 6960-2025 artfynd.xlsx
@@ -1005,54 +1005,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126003878</v>
+        <v>126003891</v>
       </c>
       <c r="B5" t="n">
-        <v>98339</v>
+        <v>99036</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>222322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Burs 1:3 (1), Gtl</t>
+          <t>Butrajvs 1:15 (2), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720409</v>
+        <v>720349</v>
       </c>
       <c r="R5" t="n">
-        <v>6383367</v>
+        <v>6383491</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1085,6 +1085,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,7 +1121,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126003891</v>
+        <v>126003884</v>
       </c>
       <c r="B6" t="n">
         <v>99036</v>
@@ -1146,7 +1151,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1160,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720349</v>
+        <v>720341</v>
       </c>
       <c r="R6" t="n">
-        <v>6383491</v>
+        <v>6383430</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1196,11 +1201,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,54 +1232,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126003884</v>
+        <v>126003878</v>
       </c>
       <c r="B7" t="n">
-        <v>99036</v>
+        <v>98339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222322</v>
+        <v>219798</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Butrajvs 1:15 (2), Gtl</t>
+          <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720341</v>
+        <v>720409</v>
       </c>
       <c r="R7" t="n">
-        <v>6383430</v>
+        <v>6383367</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1997,32 +1997,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126003877</v>
+        <v>126003880</v>
       </c>
       <c r="B14" t="n">
-        <v>98339</v>
+        <v>109185</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720418</v>
+        <v>720395</v>
       </c>
       <c r="R14" t="n">
-        <v>6383301</v>
+        <v>6383383</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2070,6 +2070,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2081,7 +2086,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Tallsumpskog med en, blåtåtel.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2099,32 +2104,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126003880</v>
+        <v>126003877</v>
       </c>
       <c r="B15" t="n">
-        <v>109185</v>
+        <v>98339</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2134,10 +2139,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720395</v>
+        <v>720418</v>
       </c>
       <c r="R15" t="n">
-        <v>6383383</v>
+        <v>6383301</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2172,11 +2177,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Tallsumpskog med en, blåtåtel.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2536,33 +2536,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126003872</v>
+        <v>126003870</v>
       </c>
       <c r="B19" t="n">
-        <v>98272</v>
+        <v>105294</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>223578</v>
+        <v>221137</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Äkta ängsnycklar</t>
+          <t>Majviva</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata var. incarnata</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>250</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2582,7 +2586,7 @@
         <v>6383301</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2616,7 +2620,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Tre mörkblommiga.</t>
+          <t>Uppskattat antal.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2648,37 +2652,33 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126003870</v>
+        <v>126003872</v>
       </c>
       <c r="B20" t="n">
-        <v>105294</v>
+        <v>98272</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221137</v>
+        <v>223578</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Majviva</t>
+          <t>Äkta ängsnycklar</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Primula farinosa</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Dactylorhiza incarnata var. incarnata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2698,7 +2698,7 @@
         <v>6383301</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Uppskattat antal.</t>
+          <t>Tre mörkblommiga.</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 6960-2025 artfynd.xlsx
+++ b/artfynd/A 6960-2025 artfynd.xlsx
@@ -1997,32 +1997,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126003880</v>
+        <v>126003877</v>
       </c>
       <c r="B14" t="n">
-        <v>109185</v>
+        <v>98339</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720395</v>
+        <v>720418</v>
       </c>
       <c r="R14" t="n">
-        <v>6383383</v>
+        <v>6383301</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2070,11 +2070,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2086,7 +2081,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Tallsumpskog med en, blåtåtel.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2104,32 +2099,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126003877</v>
+        <v>126003880</v>
       </c>
       <c r="B15" t="n">
-        <v>98339</v>
+        <v>109185</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2139,10 +2134,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720418</v>
+        <v>720395</v>
       </c>
       <c r="R15" t="n">
-        <v>6383301</v>
+        <v>6383383</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2177,6 +2172,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Tallsumpskog med en, blåtåtel.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>

--- a/artfynd/A 6960-2025 artfynd.xlsx
+++ b/artfynd/A 6960-2025 artfynd.xlsx
@@ -1005,54 +1005,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126003891</v>
+        <v>126003878</v>
       </c>
       <c r="B5" t="n">
-        <v>99036</v>
+        <v>98339</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222322</v>
+        <v>219798</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Butrajvs 1:15 (2), Gtl</t>
+          <t>Burs 1:3 (1), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720349</v>
+        <v>720409</v>
       </c>
       <c r="R5" t="n">
-        <v>6383491</v>
+        <v>6383367</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1085,11 +1085,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,7 +1116,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126003884</v>
+        <v>126003891</v>
       </c>
       <c r="B6" t="n">
         <v>99036</v>
@@ -1151,7 +1146,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1165,10 +1160,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720341</v>
+        <v>720349</v>
       </c>
       <c r="R6" t="n">
-        <v>6383430</v>
+        <v>6383491</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1201,6 +1196,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Minsta antal.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,54 +1232,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126003878</v>
+        <v>126003884</v>
       </c>
       <c r="B7" t="n">
-        <v>98339</v>
+        <v>99036</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219798</v>
+        <v>222322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Burs 1:3 (1), Gtl</t>
+          <t>Butrajvs 1:15 (2), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720409</v>
+        <v>720341</v>
       </c>
       <c r="R7" t="n">
-        <v>6383367</v>
+        <v>6383430</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1997,32 +1997,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126003877</v>
+        <v>126003880</v>
       </c>
       <c r="B14" t="n">
-        <v>98339</v>
+        <v>109185</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219798</v>
+        <v>220299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2032,10 +2032,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>720418</v>
+        <v>720395</v>
       </c>
       <c r="R14" t="n">
-        <v>6383301</v>
+        <v>6383383</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2070,6 +2070,11 @@
           <t>2025-06-12</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2081,7 +2086,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Kalkgräsmyr.</t>
+          <t>Tallsumpskog med en, blåtåtel.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2099,32 +2104,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126003880</v>
+        <v>126003877</v>
       </c>
       <c r="B15" t="n">
-        <v>109185</v>
+        <v>98339</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220299</v>
+        <v>219798</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2134,10 +2139,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>720395</v>
+        <v>720418</v>
       </c>
       <c r="R15" t="n">
-        <v>6383383</v>
+        <v>6383301</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2172,11 +2177,6 @@
           <t>2025-06-12</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Tallsumpskog med en, blåtåtel.</t>
+          <t>Kalkgräsmyr.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
